--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.52854704335972</v>
+        <v>11.29838889454595</v>
       </c>
       <c r="D2" t="n">
-        <v>72.70966821304636</v>
+        <v>11.81532108462003</v>
       </c>
       <c r="E2" t="n">
-        <v>26.61877382425936</v>
+        <v>4.325550746442147</v>
       </c>
       <c r="F2" t="n">
-        <v>24.55196389551729</v>
+        <v>3.989694133021559</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.79898987322333</v>
+        <v>3.217335854398792</v>
       </c>
       <c r="D3" t="n">
-        <v>20.64785461559523</v>
+        <v>3.355276375034225</v>
       </c>
       <c r="E3" t="n">
-        <v>26.61877382425936</v>
+        <v>4.325550746442147</v>
       </c>
       <c r="F3" t="n">
-        <v>24.55196389551729</v>
+        <v>3.989694133021559</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.143302999477305</v>
+        <v>1.323286737415062</v>
       </c>
       <c r="D4" t="n">
-        <v>20.60634565017037</v>
+        <v>3.348531168152685</v>
       </c>
       <c r="E4" t="n">
-        <v>26.61877382425936</v>
+        <v>4.325550746442147</v>
       </c>
       <c r="F4" t="n">
-        <v>24.55196389551729</v>
+        <v>3.989694133021559</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
